--- a/配車入力.xlsx
+++ b/配車入力.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="配車入力" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="車両マスタ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="荷主マスタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="乗務員マスタ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="得意先マスタ" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="記入例" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -66,8 +66,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
@@ -450,23 +459,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,12 +481,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>荷主</t>
+          <t>乗務員</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>受付No</t>
+          <t>便</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -492,50 +496,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>積地</t>
+          <t>積荷</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>積時刻</t>
+          <t>得意先</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>降地</t>
+          <t>発地</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>降時刻</t>
+          <t>着地</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>品目</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>単位</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>運賃</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>高速料金</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -552,34 +531,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>車番</t>
+          <t>乗務員</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>ドライバー</t>
+          <t>主な車番</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>車種</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>最大積載(kg)</t>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>関</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>鶴田</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>伊垣</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8816</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>横須賀</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>仲林</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>海老澤</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8815</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>芳賀</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>砂押</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>小林</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8007</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>志賀</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>宇佐美</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>萩野間</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>木村</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9480</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>高橋</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5164</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>山崎</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>根本</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5159</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>安野</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3134</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>関根</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>神長</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3069</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>小堀内</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>6891</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>吉成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>山崎正二</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>石川</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>※この並び順が日報の行順になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>※車番は目安です。実際の車番は便ごとに配車入力へ。</t>
         </is>
       </c>
     </row>
@@ -594,22 +802,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>荷主(略称)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>正式名称</t>
+          <t>得意先</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>エアウォーター</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>豊総合物流</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ロードリーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>大晴通商</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>光洋運輸</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>行方運送</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>東亜物産</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OOCL</t>
         </is>
       </c>
     </row>
@@ -624,23 +889,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,12 +911,12 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>荷主</t>
+          <t>乗務員</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>受付No</t>
+          <t>便</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -666,50 +926,25 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>積地</t>
+          <t>積荷</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>積時刻</t>
+          <t>得意先</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>降地</t>
+          <t>発地</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>降時刻</t>
+          <t>着地</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>品目</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>単位</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>運賃</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>高速料金</t>
-        </is>
-      </c>
-      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -723,57 +958,36 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>日進運輸</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A-101</t>
-        </is>
+          <t>関</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>5022</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>宇都宮工場</t>
+          <t>玉ねぎ</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>鈴与</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>川崎倉庫</t>
+          <t>日立</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>鋼材</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>48000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>豊洲</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -783,54 +997,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>日進運輸</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A-102</t>
-        </is>
+          <t>関</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>5022</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>川崎倉庫</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>鈴与</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>宇都宮工場</t>
+          <t>桶川市</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>空</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3200</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>復便</t>
-        </is>
-      </c>
+          <t>常陸那珂</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -840,70 +1036,212 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>北関ロジ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>H-21</t>
-        </is>
+          <t>芳賀</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1956</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>足利工場</t>
+          <t>チーズ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>鈴与</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>三郷DC</t>
+          <t>日立</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>紙製品</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>61000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>車両手配中</t>
-        </is>
-      </c>
+          <t>阿見</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>芳賀</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>代用乳</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>高崎市</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>日立</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>※このシートは見本です。実際の入力は『配車入力』シートへ。</t>
-        </is>
-      </c>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>芳賀</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1956</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>紙製品</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>いわき市</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>常陸那珂</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>※車番を空欄にすると日報で「未配車」として赤く出ます（配車漏れ確認用）。</t>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>伊垣</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8816</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>トマト</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>豊総合物流</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>大洗</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>着地未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026/9/10</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>玉葱</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>大晴通商</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>日立</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>豊洲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>乗務員未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>※このシートは見本です。実際の入力は『配車入力』シートへ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※便＝1便目・2便目。日報では1便目が左、2便目以降が右に並びます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>※乗務員を空欄にすると日報の最後に「未配車」として赤く出ます。</t>
         </is>
       </c>
     </row>

--- a/配車入力.xlsx
+++ b/配車入力.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="配車入力" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="乗務員マスタ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="得意先マスタ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="記入例" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="車番マスタ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="得意先マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="記入例" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +98,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,13 +472,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -479,41 +488,41 @@
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>車番</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>積荷</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>得意先</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>発地</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>着地</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>乗務員</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>便</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>車番</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>積荷</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>得意先</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>発地</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>着地</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>備考</t>
@@ -521,6 +530,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='車番マスタ'!$A$2:$A$200</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='得意先マスタ'!$A$2:$A$100</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -531,26 +548,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>乗務員</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>主な車番</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -562,9 +573,6 @@
           <t>関</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>5022</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -572,9 +580,6 @@
           <t>鶴田</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2039</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,9 +587,6 @@
           <t>伊垣</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>8816</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,9 +594,6 @@
           <t>横須賀</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>2185</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -602,9 +601,6 @@
           <t>仲林</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1464</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -612,9 +608,6 @@
           <t>海老澤</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>8815</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -622,9 +615,6 @@
           <t>芳賀</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1956</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -632,9 +622,6 @@
           <t>砂押</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1107</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -642,9 +629,6 @@
           <t>小林</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>8007</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -652,9 +636,6 @@
           <t>志賀</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>2145</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -662,9 +643,6 @@
           <t>宇佐美</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1957</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -672,9 +650,6 @@
           <t>萩野間</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1925</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -682,9 +657,6 @@
           <t>木村</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>9480</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -692,9 +664,6 @@
           <t>高橋</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>5164</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -702,9 +671,6 @@
           <t>山崎</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1523</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -712,9 +678,6 @@
           <t>根本</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>5159</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -722,9 +685,6 @@
           <t>安野</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>3134</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -732,9 +692,6 @@
           <t>関根</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -742,9 +699,6 @@
           <t>神長</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>3069</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -752,9 +706,6 @@
           <t>小堀内</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>6891</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -781,13 +732,6 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>※この並び順が日報の行順になります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>※車番は目安です。実際の車番は便ごとに配車入力へ。</t>
         </is>
       </c>
     </row>
@@ -797,6 +741,290 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>車番</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>乗務員</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5022</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>関</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2039</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>鶴田</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8816</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>伊垣</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2185</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>横須賀</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>仲林</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>仲林</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8815</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>海老澤</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3655</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>海老澤</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1956</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>芳賀</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>砂押</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8007</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>小林</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2145</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>志賀</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1957</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>宇佐美</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5135</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>宇佐美</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1925</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>萩野間</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9480</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>木村</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1983</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>木村</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>5164</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>高橋</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1523</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>山崎</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>5159</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>根本</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>安野</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>関根</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3069</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>神長</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6891</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>小堀内</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>※車番を打つと乗務員が自動で決まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>※代車で普段と違う人が乗る日は、配車入力の乗務員欄に直接書いてください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -809,7 +1037,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>得意先</t>
         </is>
@@ -883,68 +1111,68 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>車番</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>積荷</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>得意先</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>発地</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>着地</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>乗務員</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>便</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>車番</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>積荷</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>得意先</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>発地</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>着地</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -956,292 +1184,252 @@
           <t>2026/9/10</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>関</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="n">
         <v>5022</v>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>玉ねぎ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>玉ねぎ</t>
+          <t>日立</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>豊洲</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="n">
+        <v>5022</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>鈴与</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>桶川市</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>常陸那珂</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>チーズ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>日立</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>阿見</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>代用乳</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>高崎市</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>日立</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>紙製品</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>鈴与</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>いわき市</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>常陸那珂</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>8816</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>トマト</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>豊総合物流</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>大洗</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>着地未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>2403</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>雑貨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ロードリーム</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>相模原市</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>常陸那珂</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>仲林</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>代車のため乗務員を明記</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>玉葱</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>大晴通商</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>日立</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>豊洲</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>関</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>5022</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>鈴与</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>桶川市</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>常陸那珂</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>芳賀</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1956</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>チーズ</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>鈴与</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>日立</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>阿見</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>芳賀</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1956</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>代用乳</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>鈴与</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>高崎市</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>日立</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>芳賀</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1956</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>紙製品</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>鈴与</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>いわき市</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>常陸那珂</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>伊垣</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>8816</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>トマト</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>豊総合物流</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>大洗</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>着地未定</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026/9/10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>玉葱</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>大晴通商</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>日立</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>豊洲</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>乗務員未定</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>車番未定→未配車に出る</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>※このシートは見本です。実際の入力は『配車入力』シートへ。</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>※便＝1便目・2便目。日報では1便目が左、2便目以降が右に並びます。</t>
+          <t>※打ち込むのは黄色の5列（車番・積荷・得意先・発地・着地）だけです。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>※乗務員を空欄にすると日報の最後に「未配車」として赤く出ます。</t>
+          <t>※日付は1日の先頭行に1回書けば、下の行は同じ日付になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>※乗務員は車番マスタから自動で入ります。代車の日だけ手で書いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>※便は同じ乗務員の中で上から順に1便目・2便目…になります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>※車番を空欄にすると日報の最後に「未配車」として赤く出ます。</t>
         </is>
       </c>
     </row>

--- a/配車入力.xlsx
+++ b/配車入力.xlsx
@@ -532,10 +532,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='車番マスタ'!$A$2:$A$200</formula1>
+      <formula1>'車番マスタ'!$A$2:$A$200</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='得意先マスタ'!$A$2:$A$100</formula1>
+      <formula1>'得意先マスタ'!$A$2:$A$100</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
